--- a/giro_da_praça_ofertas - TERÇA.xlsx
+++ b/giro_da_praça_ofertas - TERÇA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{525D818F-FD20-459A-BD3F-270763AEF915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0282167-BAAF-432E-8835-C769F864031C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="41">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -40,6 +40,45 @@
     <t>PROMOÇÃO</t>
   </si>
   <si>
+    <t>SEGUNDA E TERCA - PERECIVEIS 28 E 29/09/26 MATRIZ</t>
+  </si>
+  <si>
+    <t>#02 MERCEARIA - CONGELADOS - BATATAS</t>
+  </si>
+  <si>
+    <t>BATATAS CONGELADAS BOUA PCT 400G PRE-FRITAS</t>
+  </si>
+  <si>
+    <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
+  </si>
+  <si>
+    <t>MANTEIGA COMUM GRANSELETTO 200G COM SAL</t>
+  </si>
+  <si>
+    <t>MARGARINA DELICIA 1KG COM CREME DE LEITE</t>
+  </si>
+  <si>
+    <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUEIJO MUSSARELA PIRACANJUBA 150G FATIADO </t>
+  </si>
+  <si>
+    <t>REQUEIJAO CREMOSO TIROLEZ 200G</t>
+  </si>
+  <si>
+    <t>#03 AÇOUGUE - #01 AVES</t>
+  </si>
+  <si>
+    <t>COXINHA DA ASA DE FRANGO SADIA PCT 1KG DRUMETE</t>
+  </si>
+  <si>
+    <t>FILE PEITO DE FRANGO SADIA PCT 1KG</t>
+  </si>
+  <si>
+    <t>FRANGO DE PADARIA SEARA 1KG A PASSARINHO</t>
+  </si>
+  <si>
     <t>TERCA - ACOUGUE 29/09/26 MATRIZ</t>
   </si>
   <si>
@@ -71,6 +110,39 @@
   </si>
   <si>
     <t>SUINO CAIPIRA KG</t>
+  </si>
+  <si>
+    <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+  </si>
+  <si>
+    <t>APRESUNTADO PERDIGÃO 200G FATIADO</t>
+  </si>
+  <si>
+    <t>LINGUIÇA DE BACON SEARA 600G TERMO</t>
+  </si>
+  <si>
+    <t>LINGUIÇA DE PERNIL PERDIGÃO 700G NA BRASA</t>
+  </si>
+  <si>
+    <t>LINGUIÇA MISTA FININHA DEFUMADA SADIA 215G</t>
+  </si>
+  <si>
+    <t>LINGUIÇA SUPER FRANGO 400G DEFUMADA</t>
+  </si>
+  <si>
+    <t>MORTADELA SUÍNA SADIA 1KG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALAME PERDIGÃO 100GR FATIADO </t>
+  </si>
+  <si>
+    <t>#03 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
+  </si>
+  <si>
+    <t>STEAK EMPANADO SADIA 100G FRANGO</t>
+  </si>
+  <si>
+    <t>TEKITOS SEARA 300G QUEIJO COM OREGANO</t>
   </si>
 </sst>
 </file>
@@ -80,7 +152,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,21 +172,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -158,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -166,22 +248,26 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -484,182 +570,495 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.28515625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="72" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
+        <v>193650</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5">
+        <v>289484</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="5">
+        <v>276943</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="5">
+        <v>158733</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5">
+        <v>104770</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="8">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="5">
+        <v>108785</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="5">
+        <v>108856</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8">
+        <v>27.99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="5">
+        <v>298984</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="5">
         <v>157014</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="D11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="8">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3">
+    <row r="12" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="5">
         <v>105470</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7">
+      <c r="D12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="8">
         <v>27.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3">
+    <row r="13" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="5">
         <v>322584</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="D13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8">
         <v>44.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3">
+    <row r="14" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="5">
         <v>105435</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="D14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8">
         <v>43.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="3">
+    <row r="15" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="5">
         <v>106065</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="D15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="7"/>
+      <c r="F15" s="8">
         <v>14.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="3">
+    <row r="16" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="5">
         <v>107260</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="D16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8">
         <v>35.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="3">
+    <row r="17" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="5">
         <v>105062</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7">
+      <c r="D17" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="7"/>
+      <c r="F17" s="8">
         <v>22.99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="3">
+    <row r="18" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="5">
         <v>298422</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="D18" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="7"/>
+      <c r="F18" s="8">
         <v>23.99</v>
       </c>
     </row>
+    <row r="19" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="5">
+        <v>272009</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="7"/>
+      <c r="F19" s="8">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="5">
+        <v>332652</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="7"/>
+      <c r="F20" s="8">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="5">
+        <v>341363</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="7"/>
+      <c r="F21" s="8">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="5">
+        <v>289127</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="7"/>
+      <c r="F22" s="8">
+        <v>8.49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="5">
+        <v>292399</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="7"/>
+      <c r="F23" s="8">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="5">
+        <v>108558</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="7"/>
+      <c r="F24" s="8">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="5">
+        <v>184045</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="7"/>
+      <c r="F25" s="8">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="5">
+        <v>170464</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="7"/>
+      <c r="F26" s="8">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="5">
+        <v>127328</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="7"/>
+      <c r="F27" s="8">
+        <v>8.99</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;LGIRO DA PRAÇA - TERÇA&amp;C&amp;P - &amp;N</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>